--- a/files/temp_files/statement_2025_08.xlsx
+++ b/files/temp_files/statement_2025_08.xlsx
@@ -597,7 +597,7 @@
         <v>35</v>
       </c>
       <c r="C2">
-        <v>89.48</v>
+        <v>-89.48</v>
       </c>
       <c r="D2" t="s">
         <v>59</v>
@@ -611,7 +611,7 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>22.16</v>
+        <v>-22.16</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
@@ -625,7 +625,7 @@
         <v>37</v>
       </c>
       <c r="C4">
-        <v>5.12</v>
+        <v>-5.12</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -639,7 +639,7 @@
         <v>38</v>
       </c>
       <c r="C5">
-        <v>16.18</v>
+        <v>-16.18</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -653,7 +653,7 @@
         <v>39</v>
       </c>
       <c r="C6">
-        <v>52.75</v>
+        <v>-52.75</v>
       </c>
       <c r="D6" t="s">
         <v>61</v>
@@ -667,7 +667,7 @@
         <v>40</v>
       </c>
       <c r="C7">
-        <v>159.79</v>
+        <v>-159.79</v>
       </c>
       <c r="D7" t="s">
         <v>62</v>
@@ -681,7 +681,7 @@
         <v>41</v>
       </c>
       <c r="C8">
-        <v>264.15</v>
+        <v>-264.15</v>
       </c>
       <c r="D8" t="s">
         <v>63</v>
@@ -695,7 +695,7 @@
         <v>42</v>
       </c>
       <c r="C9">
-        <v>212.26</v>
+        <v>-212.26</v>
       </c>
       <c r="D9" t="s">
         <v>64</v>
@@ -709,7 +709,7 @@
         <v>43</v>
       </c>
       <c r="C10">
-        <v>272.2</v>
+        <v>-272.2</v>
       </c>
       <c r="D10" t="s">
         <v>64</v>
@@ -737,7 +737,7 @@
         <v>45</v>
       </c>
       <c r="C12">
-        <v>57.68</v>
+        <v>-57.68</v>
       </c>
       <c r="D12" t="s">
         <v>66</v>
@@ -751,7 +751,7 @@
         <v>38</v>
       </c>
       <c r="C13">
-        <v>106.14</v>
+        <v>-106.14</v>
       </c>
       <c r="D13" t="s">
         <v>61</v>
@@ -765,7 +765,7 @@
         <v>46</v>
       </c>
       <c r="C14">
-        <v>242.74</v>
+        <v>-242.74</v>
       </c>
       <c r="D14" t="s">
         <v>62</v>
@@ -807,7 +807,7 @@
         <v>42</v>
       </c>
       <c r="C17">
-        <v>922.1</v>
+        <v>-922.1</v>
       </c>
       <c r="D17" t="s">
         <v>64</v>
@@ -821,7 +821,7 @@
         <v>48</v>
       </c>
       <c r="C18">
-        <v>64.42</v>
+        <v>-64.42</v>
       </c>
       <c r="D18" t="s">
         <v>66</v>
@@ -835,7 +835,7 @@
         <v>49</v>
       </c>
       <c r="C19">
-        <v>396.96</v>
+        <v>-396.96</v>
       </c>
       <c r="D19" t="s">
         <v>62</v>
@@ -849,7 +849,7 @@
         <v>39</v>
       </c>
       <c r="C20">
-        <v>70.12</v>
+        <v>-70.12</v>
       </c>
       <c r="D20" t="s">
         <v>61</v>
@@ -863,7 +863,7 @@
         <v>46</v>
       </c>
       <c r="C21">
-        <v>35.77</v>
+        <v>-35.77</v>
       </c>
       <c r="D21" t="s">
         <v>62</v>
@@ -877,7 +877,7 @@
         <v>46</v>
       </c>
       <c r="C22">
-        <v>414.45</v>
+        <v>-414.45</v>
       </c>
       <c r="D22" t="s">
         <v>62</v>
@@ -891,7 +891,7 @@
         <v>41</v>
       </c>
       <c r="C23">
-        <v>61.48</v>
+        <v>-61.48</v>
       </c>
       <c r="D23" t="s">
         <v>63</v>
@@ -905,7 +905,7 @@
         <v>45</v>
       </c>
       <c r="C24">
-        <v>95.36</v>
+        <v>-95.36</v>
       </c>
       <c r="D24" t="s">
         <v>66</v>
@@ -919,7 +919,7 @@
         <v>49</v>
       </c>
       <c r="C25">
-        <v>57.78</v>
+        <v>-57.78</v>
       </c>
       <c r="D25" t="s">
         <v>62</v>
@@ -933,7 +933,7 @@
         <v>50</v>
       </c>
       <c r="C26">
-        <v>41.03</v>
+        <v>-41.03</v>
       </c>
       <c r="D26" t="s">
         <v>60</v>
@@ -947,7 +947,7 @@
         <v>51</v>
       </c>
       <c r="C27">
-        <v>14.25</v>
+        <v>-14.25</v>
       </c>
       <c r="D27" t="s">
         <v>64</v>
@@ -961,7 +961,7 @@
         <v>37</v>
       </c>
       <c r="C28">
-        <v>29.97</v>
+        <v>-29.97</v>
       </c>
       <c r="D28" t="s">
         <v>60</v>
@@ -975,7 +975,7 @@
         <v>52</v>
       </c>
       <c r="C29">
-        <v>57.72</v>
+        <v>-57.72</v>
       </c>
       <c r="D29" t="s">
         <v>66</v>
@@ -1003,7 +1003,7 @@
         <v>39</v>
       </c>
       <c r="C31">
-        <v>195.28</v>
+        <v>-195.28</v>
       </c>
       <c r="D31" t="s">
         <v>61</v>
@@ -1017,7 +1017,7 @@
         <v>50</v>
       </c>
       <c r="C32">
-        <v>42.36</v>
+        <v>-42.36</v>
       </c>
       <c r="D32" t="s">
         <v>60</v>
@@ -1031,7 +1031,7 @@
         <v>51</v>
       </c>
       <c r="C33">
-        <v>667.6</v>
+        <v>-667.6</v>
       </c>
       <c r="D33" t="s">
         <v>64</v>
@@ -1045,7 +1045,7 @@
         <v>40</v>
       </c>
       <c r="C34">
-        <v>6.78</v>
+        <v>-6.78</v>
       </c>
       <c r="D34" t="s">
         <v>62</v>
@@ -1073,7 +1073,7 @@
         <v>45</v>
       </c>
       <c r="C36">
-        <v>72.05</v>
+        <v>-72.05</v>
       </c>
       <c r="D36" t="s">
         <v>66</v>
@@ -1087,7 +1087,7 @@
         <v>46</v>
       </c>
       <c r="C37">
-        <v>50.21</v>
+        <v>-50.21</v>
       </c>
       <c r="D37" t="s">
         <v>62</v>
@@ -1101,7 +1101,7 @@
         <v>37</v>
       </c>
       <c r="C38">
-        <v>19.86</v>
+        <v>-19.86</v>
       </c>
       <c r="D38" t="s">
         <v>60</v>
@@ -1115,7 +1115,7 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>46.62</v>
+        <v>-46.62</v>
       </c>
       <c r="D39" t="s">
         <v>61</v>
@@ -1129,7 +1129,7 @@
         <v>42</v>
       </c>
       <c r="C40">
-        <v>855.84</v>
+        <v>-855.84</v>
       </c>
       <c r="D40" t="s">
         <v>64</v>
@@ -1143,7 +1143,7 @@
         <v>37</v>
       </c>
       <c r="C41">
-        <v>35.61</v>
+        <v>-35.61</v>
       </c>
       <c r="D41" t="s">
         <v>60</v>
@@ -1171,7 +1171,7 @@
         <v>37</v>
       </c>
       <c r="C43">
-        <v>32.41</v>
+        <v>-32.41</v>
       </c>
       <c r="D43" t="s">
         <v>60</v>
@@ -1185,7 +1185,7 @@
         <v>54</v>
       </c>
       <c r="C44">
-        <v>135.73</v>
+        <v>-135.73</v>
       </c>
       <c r="D44" t="s">
         <v>61</v>
@@ -1227,7 +1227,7 @@
         <v>45</v>
       </c>
       <c r="C47">
-        <v>28.11</v>
+        <v>-28.11</v>
       </c>
       <c r="D47" t="s">
         <v>66</v>
@@ -1241,7 +1241,7 @@
         <v>52</v>
       </c>
       <c r="C48">
-        <v>36.81</v>
+        <v>-36.81</v>
       </c>
       <c r="D48" t="s">
         <v>66</v>
@@ -1255,7 +1255,7 @@
         <v>35</v>
       </c>
       <c r="C49">
-        <v>82.27</v>
+        <v>-82.27</v>
       </c>
       <c r="D49" t="s">
         <v>59</v>
@@ -1269,7 +1269,7 @@
         <v>35</v>
       </c>
       <c r="C50">
-        <v>89.87</v>
+        <v>-89.87</v>
       </c>
       <c r="D50" t="s">
         <v>59</v>
@@ -1311,7 +1311,7 @@
         <v>50</v>
       </c>
       <c r="C53">
-        <v>43.04</v>
+        <v>-43.04</v>
       </c>
       <c r="D53" t="s">
         <v>60</v>
@@ -1325,7 +1325,7 @@
         <v>54</v>
       </c>
       <c r="C54">
-        <v>169.57</v>
+        <v>-169.57</v>
       </c>
       <c r="D54" t="s">
         <v>61</v>
@@ -1339,7 +1339,7 @@
         <v>43</v>
       </c>
       <c r="C55">
-        <v>406.37</v>
+        <v>-406.37</v>
       </c>
       <c r="D55" t="s">
         <v>64</v>
@@ -1353,7 +1353,7 @@
         <v>41</v>
       </c>
       <c r="C56">
-        <v>84.91</v>
+        <v>-84.91</v>
       </c>
       <c r="D56" t="s">
         <v>63</v>
@@ -1367,7 +1367,7 @@
         <v>55</v>
       </c>
       <c r="C57">
-        <v>80.65000000000001</v>
+        <v>-80.65000000000001</v>
       </c>
       <c r="D57" t="s">
         <v>63</v>
@@ -1381,7 +1381,7 @@
         <v>56</v>
       </c>
       <c r="C58">
-        <v>89.31</v>
+        <v>-89.31</v>
       </c>
       <c r="D58" t="s">
         <v>63</v>
@@ -1395,7 +1395,7 @@
         <v>42</v>
       </c>
       <c r="C59">
-        <v>92.45999999999999</v>
+        <v>-92.45999999999999</v>
       </c>
       <c r="D59" t="s">
         <v>64</v>
@@ -1409,7 +1409,7 @@
         <v>56</v>
       </c>
       <c r="C60">
-        <v>135.61</v>
+        <v>-135.61</v>
       </c>
       <c r="D60" t="s">
         <v>63</v>
@@ -1423,7 +1423,7 @@
         <v>51</v>
       </c>
       <c r="C61">
-        <v>464.33</v>
+        <v>-464.33</v>
       </c>
       <c r="D61" t="s">
         <v>64</v>
@@ -1437,7 +1437,7 @@
         <v>39</v>
       </c>
       <c r="C62">
-        <v>101.83</v>
+        <v>-101.83</v>
       </c>
       <c r="D62" t="s">
         <v>61</v>
@@ -1451,7 +1451,7 @@
         <v>42</v>
       </c>
       <c r="C63">
-        <v>239.1</v>
+        <v>-239.1</v>
       </c>
       <c r="D63" t="s">
         <v>64</v>
@@ -1465,7 +1465,7 @@
         <v>35</v>
       </c>
       <c r="C64">
-        <v>26.97</v>
+        <v>-26.97</v>
       </c>
       <c r="D64" t="s">
         <v>59</v>
@@ -1479,7 +1479,7 @@
         <v>55</v>
       </c>
       <c r="C65">
-        <v>251.76</v>
+        <v>-251.76</v>
       </c>
       <c r="D65" t="s">
         <v>63</v>
@@ -1493,7 +1493,7 @@
         <v>41</v>
       </c>
       <c r="C66">
-        <v>81.81999999999999</v>
+        <v>-81.81999999999999</v>
       </c>
       <c r="D66" t="s">
         <v>63</v>
@@ -1507,7 +1507,7 @@
         <v>57</v>
       </c>
       <c r="C67">
-        <v>48.07</v>
+        <v>-48.07</v>
       </c>
       <c r="D67" t="s">
         <v>59</v>
@@ -1521,7 +1521,7 @@
         <v>35</v>
       </c>
       <c r="C68">
-        <v>81.88</v>
+        <v>-81.88</v>
       </c>
       <c r="D68" t="s">
         <v>59</v>
@@ -1535,7 +1535,7 @@
         <v>50</v>
       </c>
       <c r="C69">
-        <v>49.85</v>
+        <v>-49.85</v>
       </c>
       <c r="D69" t="s">
         <v>60</v>
@@ -1549,7 +1549,7 @@
         <v>36</v>
       </c>
       <c r="C70">
-        <v>13.43</v>
+        <v>-13.43</v>
       </c>
       <c r="D70" t="s">
         <v>60</v>
@@ -1563,7 +1563,7 @@
         <v>40</v>
       </c>
       <c r="C71">
-        <v>80.43000000000001</v>
+        <v>-80.43000000000001</v>
       </c>
       <c r="D71" t="s">
         <v>62</v>
@@ -1577,7 +1577,7 @@
         <v>38</v>
       </c>
       <c r="C72">
-        <v>103.02</v>
+        <v>-103.02</v>
       </c>
       <c r="D72" t="s">
         <v>61</v>
@@ -1591,7 +1591,7 @@
         <v>54</v>
       </c>
       <c r="C73">
-        <v>95.47</v>
+        <v>-95.47</v>
       </c>
       <c r="D73" t="s">
         <v>61</v>
@@ -1605,7 +1605,7 @@
         <v>43</v>
       </c>
       <c r="C74">
-        <v>29.53</v>
+        <v>-29.53</v>
       </c>
       <c r="D74" t="s">
         <v>64</v>
@@ -1619,7 +1619,7 @@
         <v>49</v>
       </c>
       <c r="C75">
-        <v>461.28</v>
+        <v>-461.28</v>
       </c>
       <c r="D75" t="s">
         <v>62</v>
@@ -1633,7 +1633,7 @@
         <v>42</v>
       </c>
       <c r="C76">
-        <v>579.15</v>
+        <v>-579.15</v>
       </c>
       <c r="D76" t="s">
         <v>64</v>
@@ -1647,7 +1647,7 @@
         <v>55</v>
       </c>
       <c r="C77">
-        <v>193.96</v>
+        <v>-193.96</v>
       </c>
       <c r="D77" t="s">
         <v>63</v>
@@ -1675,7 +1675,7 @@
         <v>40</v>
       </c>
       <c r="C79">
-        <v>476.14</v>
+        <v>-476.14</v>
       </c>
       <c r="D79" t="s">
         <v>62</v>
@@ -1703,7 +1703,7 @@
         <v>51</v>
       </c>
       <c r="C81">
-        <v>494.02</v>
+        <v>-494.02</v>
       </c>
       <c r="D81" t="s">
         <v>64</v>
@@ -1717,7 +1717,7 @@
         <v>52</v>
       </c>
       <c r="C82">
-        <v>71.58</v>
+        <v>-71.58</v>
       </c>
       <c r="D82" t="s">
         <v>66</v>
@@ -1731,7 +1731,7 @@
         <v>49</v>
       </c>
       <c r="C83">
-        <v>67.06999999999999</v>
+        <v>-67.06999999999999</v>
       </c>
       <c r="D83" t="s">
         <v>62</v>
@@ -1745,7 +1745,7 @@
         <v>37</v>
       </c>
       <c r="C84">
-        <v>41.79</v>
+        <v>-41.79</v>
       </c>
       <c r="D84" t="s">
         <v>60</v>
@@ -1759,7 +1759,7 @@
         <v>40</v>
       </c>
       <c r="C85">
-        <v>409.49</v>
+        <v>-409.49</v>
       </c>
       <c r="D85" t="s">
         <v>62</v>
@@ -1773,7 +1773,7 @@
         <v>51</v>
       </c>
       <c r="C86">
-        <v>947.11</v>
+        <v>-947.11</v>
       </c>
       <c r="D86" t="s">
         <v>64</v>
@@ -1787,7 +1787,7 @@
         <v>38</v>
       </c>
       <c r="C87">
-        <v>99.11</v>
+        <v>-99.11</v>
       </c>
       <c r="D87" t="s">
         <v>61</v>
@@ -1801,7 +1801,7 @@
         <v>39</v>
       </c>
       <c r="C88">
-        <v>98.28</v>
+        <v>-98.28</v>
       </c>
       <c r="D88" t="s">
         <v>61</v>
@@ -1815,7 +1815,7 @@
         <v>37</v>
       </c>
       <c r="C89">
-        <v>34.75</v>
+        <v>-34.75</v>
       </c>
       <c r="D89" t="s">
         <v>60</v>
@@ -1829,7 +1829,7 @@
         <v>50</v>
       </c>
       <c r="C90">
-        <v>48.29</v>
+        <v>-48.29</v>
       </c>
       <c r="D90" t="s">
         <v>60</v>
@@ -1843,7 +1843,7 @@
         <v>49</v>
       </c>
       <c r="C91">
-        <v>205.04</v>
+        <v>-205.04</v>
       </c>
       <c r="D91" t="s">
         <v>62</v>
@@ -1857,7 +1857,7 @@
         <v>36</v>
       </c>
       <c r="C92">
-        <v>32.12</v>
+        <v>-32.12</v>
       </c>
       <c r="D92" t="s">
         <v>60</v>
@@ -1871,7 +1871,7 @@
         <v>51</v>
       </c>
       <c r="C93">
-        <v>847.33</v>
+        <v>-847.33</v>
       </c>
       <c r="D93" t="s">
         <v>64</v>
@@ -1899,7 +1899,7 @@
         <v>51</v>
       </c>
       <c r="C95">
-        <v>356.22</v>
+        <v>-356.22</v>
       </c>
       <c r="D95" t="s">
         <v>64</v>
@@ -1913,7 +1913,7 @@
         <v>36</v>
       </c>
       <c r="C96">
-        <v>18.97</v>
+        <v>-18.97</v>
       </c>
       <c r="D96" t="s">
         <v>60</v>
@@ -1927,7 +1927,7 @@
         <v>58</v>
       </c>
       <c r="C97">
-        <v>29.55</v>
+        <v>-29.55</v>
       </c>
       <c r="D97" t="s">
         <v>59</v>
@@ -1941,7 +1941,7 @@
         <v>46</v>
       </c>
       <c r="C98">
-        <v>406.47</v>
+        <v>-406.47</v>
       </c>
       <c r="D98" t="s">
         <v>62</v>
@@ -1955,7 +1955,7 @@
         <v>54</v>
       </c>
       <c r="C99">
-        <v>183.75</v>
+        <v>-183.75</v>
       </c>
       <c r="D99" t="s">
         <v>61</v>
@@ -1969,7 +1969,7 @@
         <v>52</v>
       </c>
       <c r="C100">
-        <v>58.6</v>
+        <v>-58.6</v>
       </c>
       <c r="D100" t="s">
         <v>66</v>
@@ -1983,7 +1983,7 @@
         <v>58</v>
       </c>
       <c r="C101">
-        <v>123.25</v>
+        <v>-123.25</v>
       </c>
       <c r="D101" t="s">
         <v>59</v>
@@ -2011,7 +2011,7 @@
         <v>41</v>
       </c>
       <c r="C103">
-        <v>56.09</v>
+        <v>-56.09</v>
       </c>
       <c r="D103" t="s">
         <v>63</v>
@@ -2025,7 +2025,7 @@
         <v>46</v>
       </c>
       <c r="C104">
-        <v>77.12</v>
+        <v>-77.12</v>
       </c>
       <c r="D104" t="s">
         <v>62</v>
@@ -2039,7 +2039,7 @@
         <v>42</v>
       </c>
       <c r="C105">
-        <v>473.58</v>
+        <v>-473.58</v>
       </c>
       <c r="D105" t="s">
         <v>64</v>
@@ -2053,7 +2053,7 @@
         <v>58</v>
       </c>
       <c r="C106">
-        <v>53.06</v>
+        <v>-53.06</v>
       </c>
       <c r="D106" t="s">
         <v>59</v>
@@ -2067,7 +2067,7 @@
         <v>40</v>
       </c>
       <c r="C107">
-        <v>497.15</v>
+        <v>-497.15</v>
       </c>
       <c r="D107" t="s">
         <v>62</v>
@@ -2081,7 +2081,7 @@
         <v>56</v>
       </c>
       <c r="C108">
-        <v>139.77</v>
+        <v>-139.77</v>
       </c>
       <c r="D108" t="s">
         <v>63</v>
@@ -2109,7 +2109,7 @@
         <v>36</v>
       </c>
       <c r="C110">
-        <v>4.52</v>
+        <v>-4.52</v>
       </c>
       <c r="D110" t="s">
         <v>60</v>
@@ -2123,7 +2123,7 @@
         <v>37</v>
       </c>
       <c r="C111">
-        <v>32.67</v>
+        <v>-32.67</v>
       </c>
       <c r="D111" t="s">
         <v>60</v>
@@ -2137,7 +2137,7 @@
         <v>58</v>
       </c>
       <c r="C112">
-        <v>69.09</v>
+        <v>-69.09</v>
       </c>
       <c r="D112" t="s">
         <v>59</v>
@@ -2151,7 +2151,7 @@
         <v>58</v>
       </c>
       <c r="C113">
-        <v>78.7</v>
+        <v>-78.7</v>
       </c>
       <c r="D113" t="s">
         <v>59</v>
@@ -2165,7 +2165,7 @@
         <v>42</v>
       </c>
       <c r="C114">
-        <v>131.57</v>
+        <v>-131.57</v>
       </c>
       <c r="D114" t="s">
         <v>64</v>
@@ -2179,7 +2179,7 @@
         <v>54</v>
       </c>
       <c r="C115">
-        <v>161.44</v>
+        <v>-161.44</v>
       </c>
       <c r="D115" t="s">
         <v>61</v>
@@ -2193,7 +2193,7 @@
         <v>56</v>
       </c>
       <c r="C116">
-        <v>278.11</v>
+        <v>-278.11</v>
       </c>
       <c r="D116" t="s">
         <v>63</v>
@@ -2207,7 +2207,7 @@
         <v>42</v>
       </c>
       <c r="C117">
-        <v>3.8</v>
+        <v>-3.8</v>
       </c>
       <c r="D117" t="s">
         <v>64</v>
@@ -2277,7 +2277,7 @@
         <v>58</v>
       </c>
       <c r="C122">
-        <v>36.45</v>
+        <v>-36.45</v>
       </c>
       <c r="D122" t="s">
         <v>59</v>
@@ -2291,7 +2291,7 @@
         <v>36</v>
       </c>
       <c r="C123">
-        <v>33.57</v>
+        <v>-33.57</v>
       </c>
       <c r="D123" t="s">
         <v>60</v>
@@ -2305,7 +2305,7 @@
         <v>41</v>
       </c>
       <c r="C124">
-        <v>264.91</v>
+        <v>-264.91</v>
       </c>
       <c r="D124" t="s">
         <v>63</v>
@@ -2333,7 +2333,7 @@
         <v>54</v>
       </c>
       <c r="C126">
-        <v>179.95</v>
+        <v>-179.95</v>
       </c>
       <c r="D126" t="s">
         <v>61</v>
@@ -2347,7 +2347,7 @@
         <v>57</v>
       </c>
       <c r="C127">
-        <v>114.22</v>
+        <v>-114.22</v>
       </c>
       <c r="D127" t="s">
         <v>59</v>
@@ -2361,7 +2361,7 @@
         <v>38</v>
       </c>
       <c r="C128">
-        <v>78.39</v>
+        <v>-78.39</v>
       </c>
       <c r="D128" t="s">
         <v>61</v>
@@ -2375,7 +2375,7 @@
         <v>48</v>
       </c>
       <c r="C129">
-        <v>45.44</v>
+        <v>-45.44</v>
       </c>
       <c r="D129" t="s">
         <v>66</v>
@@ -2389,7 +2389,7 @@
         <v>45</v>
       </c>
       <c r="C130">
-        <v>69.52</v>
+        <v>-69.52</v>
       </c>
       <c r="D130" t="s">
         <v>66</v>
@@ -2417,7 +2417,7 @@
         <v>48</v>
       </c>
       <c r="C132">
-        <v>78.08</v>
+        <v>-78.08</v>
       </c>
       <c r="D132" t="s">
         <v>66</v>
@@ -2431,7 +2431,7 @@
         <v>50</v>
       </c>
       <c r="C133">
-        <v>13.62</v>
+        <v>-13.62</v>
       </c>
       <c r="D133" t="s">
         <v>60</v>
@@ -2445,7 +2445,7 @@
         <v>57</v>
       </c>
       <c r="C134">
-        <v>85.8</v>
+        <v>-85.8</v>
       </c>
       <c r="D134" t="s">
         <v>59</v>
@@ -2459,7 +2459,7 @@
         <v>37</v>
       </c>
       <c r="C135">
-        <v>27.84</v>
+        <v>-27.84</v>
       </c>
       <c r="D135" t="s">
         <v>60</v>
@@ -2473,7 +2473,7 @@
         <v>38</v>
       </c>
       <c r="C136">
-        <v>24.5</v>
+        <v>-24.5</v>
       </c>
       <c r="D136" t="s">
         <v>61</v>
@@ -2501,7 +2501,7 @@
         <v>40</v>
       </c>
       <c r="C138">
-        <v>79.05</v>
+        <v>-79.05</v>
       </c>
       <c r="D138" t="s">
         <v>62</v>
@@ -2529,7 +2529,7 @@
         <v>57</v>
       </c>
       <c r="C140">
-        <v>145.59</v>
+        <v>-145.59</v>
       </c>
       <c r="D140" t="s">
         <v>59</v>
@@ -2543,7 +2543,7 @@
         <v>55</v>
       </c>
       <c r="C141">
-        <v>84.88</v>
+        <v>-84.88</v>
       </c>
       <c r="D141" t="s">
         <v>63</v>
@@ -2557,7 +2557,7 @@
         <v>52</v>
       </c>
       <c r="C142">
-        <v>48.31</v>
+        <v>-48.31</v>
       </c>
       <c r="D142" t="s">
         <v>66</v>
@@ -2571,7 +2571,7 @@
         <v>45</v>
       </c>
       <c r="C143">
-        <v>72.2</v>
+        <v>-72.2</v>
       </c>
       <c r="D143" t="s">
         <v>66</v>
@@ -2585,7 +2585,7 @@
         <v>52</v>
       </c>
       <c r="C144">
-        <v>69.19</v>
+        <v>-69.19</v>
       </c>
       <c r="D144" t="s">
         <v>66</v>
@@ -2599,7 +2599,7 @@
         <v>38</v>
       </c>
       <c r="C145">
-        <v>48.38</v>
+        <v>-48.38</v>
       </c>
       <c r="D145" t="s">
         <v>61</v>
@@ -2613,7 +2613,7 @@
         <v>46</v>
       </c>
       <c r="C146">
-        <v>244.15</v>
+        <v>-244.15</v>
       </c>
       <c r="D146" t="s">
         <v>62</v>
@@ -2627,7 +2627,7 @@
         <v>48</v>
       </c>
       <c r="C147">
-        <v>58.47</v>
+        <v>-58.47</v>
       </c>
       <c r="D147" t="s">
         <v>66</v>
@@ -2641,7 +2641,7 @@
         <v>52</v>
       </c>
       <c r="C148">
-        <v>57.16</v>
+        <v>-57.16</v>
       </c>
       <c r="D148" t="s">
         <v>66</v>
@@ -2655,7 +2655,7 @@
         <v>48</v>
       </c>
       <c r="C149">
-        <v>50.55</v>
+        <v>-50.55</v>
       </c>
       <c r="D149" t="s">
         <v>66</v>
@@ -2669,7 +2669,7 @@
         <v>36</v>
       </c>
       <c r="C150">
-        <v>24.86</v>
+        <v>-24.86</v>
       </c>
       <c r="D150" t="s">
         <v>60</v>
@@ -2683,7 +2683,7 @@
         <v>55</v>
       </c>
       <c r="C151">
-        <v>221.77</v>
+        <v>-221.77</v>
       </c>
       <c r="D151" t="s">
         <v>63</v>
@@ -2697,7 +2697,7 @@
         <v>54</v>
       </c>
       <c r="C152">
-        <v>177.11</v>
+        <v>-177.11</v>
       </c>
       <c r="D152" t="s">
         <v>61</v>
@@ -2711,7 +2711,7 @@
         <v>45</v>
       </c>
       <c r="C153">
-        <v>69.26000000000001</v>
+        <v>-69.26000000000001</v>
       </c>
       <c r="D153" t="s">
         <v>66</v>
@@ -2725,7 +2725,7 @@
         <v>49</v>
       </c>
       <c r="C154">
-        <v>156.37</v>
+        <v>-156.37</v>
       </c>
       <c r="D154" t="s">
         <v>62</v>
@@ -2739,7 +2739,7 @@
         <v>58</v>
       </c>
       <c r="C155">
-        <v>131.64</v>
+        <v>-131.64</v>
       </c>
       <c r="D155" t="s">
         <v>59</v>
@@ -2753,7 +2753,7 @@
         <v>39</v>
       </c>
       <c r="C156">
-        <v>159.45</v>
+        <v>-159.45</v>
       </c>
       <c r="D156" t="s">
         <v>61</v>
@@ -2781,7 +2781,7 @@
         <v>56</v>
       </c>
       <c r="C158">
-        <v>206.97</v>
+        <v>-206.97</v>
       </c>
       <c r="D158" t="s">
         <v>63</v>
@@ -2809,7 +2809,7 @@
         <v>42</v>
       </c>
       <c r="C160">
-        <v>611.6799999999999</v>
+        <v>-611.6799999999999</v>
       </c>
       <c r="D160" t="s">
         <v>64</v>
@@ -2823,7 +2823,7 @@
         <v>50</v>
       </c>
       <c r="C161">
-        <v>20.83</v>
+        <v>-20.83</v>
       </c>
       <c r="D161" t="s">
         <v>60</v>
@@ -2837,7 +2837,7 @@
         <v>36</v>
       </c>
       <c r="C162">
-        <v>5.02</v>
+        <v>-5.02</v>
       </c>
       <c r="D162" t="s">
         <v>60</v>
@@ -2851,7 +2851,7 @@
         <v>43</v>
       </c>
       <c r="C163">
-        <v>577.39</v>
+        <v>-577.39</v>
       </c>
       <c r="D163" t="s">
         <v>64</v>
@@ -2865,7 +2865,7 @@
         <v>41</v>
       </c>
       <c r="C164">
-        <v>171.3</v>
+        <v>-171.3</v>
       </c>
       <c r="D164" t="s">
         <v>63</v>
@@ -2879,7 +2879,7 @@
         <v>54</v>
       </c>
       <c r="C165">
-        <v>142.65</v>
+        <v>-142.65</v>
       </c>
       <c r="D165" t="s">
         <v>61</v>
@@ -2907,7 +2907,7 @@
         <v>38</v>
       </c>
       <c r="C167">
-        <v>29.76</v>
+        <v>-29.76</v>
       </c>
       <c r="D167" t="s">
         <v>61</v>
@@ -2921,7 +2921,7 @@
         <v>56</v>
       </c>
       <c r="C168">
-        <v>131.82</v>
+        <v>-131.82</v>
       </c>
       <c r="D168" t="s">
         <v>63</v>
@@ -2935,7 +2935,7 @@
         <v>46</v>
       </c>
       <c r="C169">
-        <v>191.12</v>
+        <v>-191.12</v>
       </c>
       <c r="D169" t="s">
         <v>62</v>
@@ -2949,7 +2949,7 @@
         <v>43</v>
       </c>
       <c r="C170">
-        <v>108.84</v>
+        <v>-108.84</v>
       </c>
       <c r="D170" t="s">
         <v>64</v>
@@ -2977,7 +2977,7 @@
         <v>55</v>
       </c>
       <c r="C172">
-        <v>239.96</v>
+        <v>-239.96</v>
       </c>
       <c r="D172" t="s">
         <v>63</v>
@@ -3005,7 +3005,7 @@
         <v>49</v>
       </c>
       <c r="C174">
-        <v>332.84</v>
+        <v>-332.84</v>
       </c>
       <c r="D174" t="s">
         <v>62</v>
@@ -3019,7 +3019,7 @@
         <v>43</v>
       </c>
       <c r="C175">
-        <v>550.37</v>
+        <v>-550.37</v>
       </c>
       <c r="D175" t="s">
         <v>64</v>
@@ -3033,7 +3033,7 @@
         <v>37</v>
       </c>
       <c r="C176">
-        <v>37.6</v>
+        <v>-37.6</v>
       </c>
       <c r="D176" t="s">
         <v>60</v>
@@ -3047,7 +3047,7 @@
         <v>38</v>
       </c>
       <c r="C177">
-        <v>22.21</v>
+        <v>-22.21</v>
       </c>
       <c r="D177" t="s">
         <v>61</v>
@@ -3061,7 +3061,7 @@
         <v>54</v>
       </c>
       <c r="C178">
-        <v>194.66</v>
+        <v>-194.66</v>
       </c>
       <c r="D178" t="s">
         <v>61</v>
@@ -3075,7 +3075,7 @@
         <v>50</v>
       </c>
       <c r="C179">
-        <v>11.65</v>
+        <v>-11.65</v>
       </c>
       <c r="D179" t="s">
         <v>60</v>
@@ -3089,7 +3089,7 @@
         <v>40</v>
       </c>
       <c r="C180">
-        <v>499.31</v>
+        <v>-499.31</v>
       </c>
       <c r="D180" t="s">
         <v>62</v>
@@ -3103,7 +3103,7 @@
         <v>58</v>
       </c>
       <c r="C181">
-        <v>63.04</v>
+        <v>-63.04</v>
       </c>
       <c r="D181" t="s">
         <v>59</v>
@@ -3117,7 +3117,7 @@
         <v>57</v>
       </c>
       <c r="C182">
-        <v>113.11</v>
+        <v>-113.11</v>
       </c>
       <c r="D182" t="s">
         <v>59</v>
@@ -3145,7 +3145,7 @@
         <v>49</v>
       </c>
       <c r="C184">
-        <v>352.07</v>
+        <v>-352.07</v>
       </c>
       <c r="D184" t="s">
         <v>62</v>
@@ -3159,7 +3159,7 @@
         <v>42</v>
       </c>
       <c r="C185">
-        <v>191.44</v>
+        <v>-191.44</v>
       </c>
       <c r="D185" t="s">
         <v>64</v>
@@ -3173,7 +3173,7 @@
         <v>58</v>
       </c>
       <c r="C186">
-        <v>57.1</v>
+        <v>-57.1</v>
       </c>
       <c r="D186" t="s">
         <v>59</v>
@@ -3187,7 +3187,7 @@
         <v>50</v>
       </c>
       <c r="C187">
-        <v>42.21</v>
+        <v>-42.21</v>
       </c>
       <c r="D187" t="s">
         <v>60</v>
@@ -3201,7 +3201,7 @@
         <v>43</v>
       </c>
       <c r="C188">
-        <v>163.62</v>
+        <v>-163.62</v>
       </c>
       <c r="D188" t="s">
         <v>64</v>
@@ -3215,7 +3215,7 @@
         <v>37</v>
       </c>
       <c r="C189">
-        <v>21.03</v>
+        <v>-21.03</v>
       </c>
       <c r="D189" t="s">
         <v>60</v>
@@ -3229,7 +3229,7 @@
         <v>42</v>
       </c>
       <c r="C190">
-        <v>685.6900000000001</v>
+        <v>-685.6900000000001</v>
       </c>
       <c r="D190" t="s">
         <v>64</v>
@@ -3299,7 +3299,7 @@
         <v>51</v>
       </c>
       <c r="C195">
-        <v>719.62</v>
+        <v>-719.62</v>
       </c>
       <c r="D195" t="s">
         <v>64</v>
@@ -3313,7 +3313,7 @@
         <v>46</v>
       </c>
       <c r="C196">
-        <v>59.97</v>
+        <v>-59.97</v>
       </c>
       <c r="D196" t="s">
         <v>62</v>
@@ -3327,7 +3327,7 @@
         <v>52</v>
       </c>
       <c r="C197">
-        <v>29.5</v>
+        <v>-29.5</v>
       </c>
       <c r="D197" t="s">
         <v>66</v>
@@ -3341,7 +3341,7 @@
         <v>55</v>
       </c>
       <c r="C198">
-        <v>174.06</v>
+        <v>-174.06</v>
       </c>
       <c r="D198" t="s">
         <v>63</v>
@@ -3355,7 +3355,7 @@
         <v>36</v>
       </c>
       <c r="C199">
-        <v>26.46</v>
+        <v>-26.46</v>
       </c>
       <c r="D199" t="s">
         <v>60</v>
@@ -3369,7 +3369,7 @@
         <v>36</v>
       </c>
       <c r="C200">
-        <v>23.59</v>
+        <v>-23.59</v>
       </c>
       <c r="D200" t="s">
         <v>60</v>
